--- a/Tính toán thông số động cơ.xlsx
+++ b/Tính toán thông số động cơ.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Inguy\OneDrive\Desktop\Tài liệu học tập\EE4332-20261\EM Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C63B21E1-4F1A-491F-939F-CD264100A34E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{778915A7-813F-47F4-AB48-BB4B35FFCEA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tính toán chi tiết động cơ a=1" sheetId="2" r:id="rId1"/>
@@ -1563,7 +1563,7 @@
   <cols>
     <col min="1" max="1" width="4.85546875" customWidth="1"/>
     <col min="2" max="2" width="40.7109375" customWidth="1"/>
-    <col min="4" max="4" width="22.42578125" customWidth="1"/>
+    <col min="4" max="4" width="25.140625" customWidth="1"/>
     <col min="5" max="5" width="12.42578125" customWidth="1"/>
     <col min="6" max="6" width="7" customWidth="1"/>
     <col min="7" max="7" width="8.42578125" customWidth="1"/>
@@ -3088,8 +3088,8 @@
   </mergeCells>
   <printOptions horizontalCentered="1" gridLines="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
-  <pageSetup fitToHeight="0" pageOrder="overThenDown" orientation="landscape" cellComments="atEnd"/>
-  <drawing r:id="rId1"/>
+  <pageSetup scale="42" fitToHeight="0" pageOrder="overThenDown" orientation="landscape" cellComments="atEnd" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
